--- a/Result/profitability/3189.xlsx
+++ b/Result/profitability/3189.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.73</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>24.3225</v>
+        <v>23.9125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.83375</v>
+        <v>1.22375</v>
       </c>
       <c r="N3" t="n">
-        <v>23.7825</v>
+        <v>23.5525</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0975</v>
+        <v>1.3425</v>
       </c>
       <c r="N4" t="n">
-        <v>23.9525</v>
+        <v>24.39875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.89</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1325</v>
+        <v>1.36125</v>
       </c>
       <c r="N5" t="n">
-        <v>25.9725</v>
+        <v>26.59875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0925</v>
+        <v>1.32</v>
       </c>
       <c r="N6" t="n">
-        <v>25.905</v>
+        <v>26.79625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.19</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1475</v>
+        <v>1.2925</v>
       </c>
       <c r="N7" t="n">
-        <v>27.69375</v>
+        <v>28.1875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.165</v>
+        <v>1.34</v>
       </c>
       <c r="N8" t="n">
-        <v>29.17625</v>
+        <v>29.7925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>12496</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9235</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3261</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1679</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>106</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1784</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1311</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8887499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.65625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.196581196581197</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2329867674858224</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.472972972972973</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.010000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2376660341555978</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
